--- a/resources/report/60/95/ex_imp/TID_111_VAT_INVOICE_C_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_111_VAT_INVOICE_C_IMP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lvthe\OneDrive\Máy tính\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4F2AF0-F73C-4DD7-80E1-5C5E6AF87614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D14BE4-63D4-4BD6-9547-E724F095D743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="5" r:id="rId1"/>
@@ -1878,6 +1878,120 @@
     <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="46" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="46" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="53" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1887,9 +2001,6 @@
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1902,121 +2013,10 @@
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="26" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="26" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="46" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="46" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2342,33 +2342,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U44"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="1.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="3.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="3.77734375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="1.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="4.33203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="0.6640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="4.6640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="0.6640625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="5.6640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="14.6640625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="1.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.33203125" style="1"/>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="1.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="1.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="0.7109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="0.7109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.7109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="1.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="4.9000000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32"/>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -2390,7 +2390,7 @@
       <c r="S1" s="32"/>
       <c r="T1" s="32"/>
     </row>
-    <row r="2" spans="1:21" ht="25.2" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="25.15" customHeight="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A2" s="33"/>
       <c r="B2" s="34"/>
       <c r="C2" s="35"/>
@@ -2398,26 +2398,26 @@
       <c r="E2" s="35"/>
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
-      <c r="H2" s="107" t="s">
+      <c r="H2" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
-      <c r="P2" s="108" t="s">
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="145" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
+      <c r="Q2" s="145"/>
+      <c r="R2" s="145"/>
+      <c r="S2" s="145"/>
       <c r="T2" s="36"/>
       <c r="U2" s="11"/>
     </row>
-    <row r="3" spans="1:21" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="37"/>
       <c r="B3" s="38"/>
       <c r="C3" s="38"/>
@@ -2425,26 +2425,26 @@
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
       <c r="G3" s="38"/>
-      <c r="H3" s="109" t="s">
+      <c r="H3" s="146" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="109"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="109"/>
-      <c r="L3" s="109"/>
-      <c r="M3" s="109"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="109"/>
-      <c r="P3" s="110" t="s">
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
+      <c r="L3" s="146"/>
+      <c r="M3" s="146"/>
+      <c r="N3" s="146"/>
+      <c r="O3" s="146"/>
+      <c r="P3" s="147" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="110"/>
-      <c r="R3" s="110"/>
-      <c r="S3" s="110"/>
+      <c r="Q3" s="147"/>
+      <c r="R3" s="147"/>
+      <c r="S3" s="147"/>
       <c r="T3" s="39"/>
       <c r="U3" s="12"/>
     </row>
-    <row r="4" spans="1:21" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="37"/>
       <c r="B4" s="38"/>
       <c r="C4" s="38"/>
@@ -2452,14 +2452,14 @@
       <c r="E4" s="38"/>
       <c r="F4" s="38"/>
       <c r="G4" s="38"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="108"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="108"/>
       <c r="P4" s="40"/>
       <c r="Q4" s="40"/>
       <c r="R4" s="40"/>
@@ -2467,7 +2467,7 @@
       <c r="T4" s="40"/>
       <c r="U4" s="12"/>
     </row>
-    <row r="5" spans="1:21" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="37"/>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
@@ -2475,15 +2475,15 @@
       <c r="E5" s="38"/>
       <c r="F5" s="38"/>
       <c r="G5" s="38"/>
-      <c r="H5" s="112" t="s">
+      <c r="H5" s="148" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="112"/>
-      <c r="J5" s="112"/>
-      <c r="K5" s="112"/>
-      <c r="L5" s="112"/>
-      <c r="M5" s="112"/>
-      <c r="N5" s="112"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="148"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
       <c r="O5" s="40"/>
       <c r="P5" s="40"/>
       <c r="Q5" s="40"/>
@@ -2492,7 +2492,7 @@
       <c r="T5" s="40"/>
       <c r="U5" s="13"/>
     </row>
-    <row r="6" spans="1:21" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="37"/>
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
@@ -2515,7 +2515,7 @@
       <c r="T6" s="40"/>
       <c r="U6" s="13"/>
     </row>
-    <row r="7" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="37"/>
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
@@ -2525,14 +2525,14 @@
         <v>46</v>
       </c>
       <c r="G7" s="70"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="113"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="113"/>
-      <c r="L7" s="113"/>
-      <c r="M7" s="113"/>
-      <c r="N7" s="113"/>
-      <c r="O7" s="113"/>
+      <c r="H7" s="149"/>
+      <c r="I7" s="149"/>
+      <c r="J7" s="149"/>
+      <c r="K7" s="149"/>
+      <c r="L7" s="149"/>
+      <c r="M7" s="149"/>
+      <c r="N7" s="149"/>
+      <c r="O7" s="149"/>
       <c r="P7" s="88"/>
       <c r="Q7" s="88"/>
       <c r="R7" s="38"/>
@@ -2540,7 +2540,7 @@
       <c r="T7" s="38"/>
       <c r="U7" s="13"/>
     </row>
-    <row r="8" spans="1:21" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="3" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="37"/>
       <c r="B8" s="41"/>
       <c r="C8" s="41"/>
@@ -2563,7 +2563,7 @@
       <c r="T8" s="38"/>
       <c r="U8" s="12"/>
     </row>
-    <row r="9" spans="1:21" ht="25.2" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="25.15" customHeight="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A9" s="43"/>
       <c r="B9" s="89" t="s">
         <v>25</v>
@@ -2575,22 +2575,22 @@
       <c r="G9" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="103"/>
-      <c r="I9" s="103"/>
-      <c r="J9" s="103"/>
-      <c r="K9" s="103"/>
-      <c r="L9" s="103"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="103"/>
-      <c r="O9" s="103"/>
-      <c r="P9" s="103"/>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="103"/>
-      <c r="S9" s="103"/>
-      <c r="T9" s="103"/>
+      <c r="H9" s="141"/>
+      <c r="I9" s="141"/>
+      <c r="J9" s="141"/>
+      <c r="K9" s="141"/>
+      <c r="L9" s="141"/>
+      <c r="M9" s="141"/>
+      <c r="N9" s="141"/>
+      <c r="O9" s="141"/>
+      <c r="P9" s="141"/>
+      <c r="Q9" s="141"/>
+      <c r="R9" s="141"/>
+      <c r="S9" s="141"/>
+      <c r="T9" s="141"/>
       <c r="U9" s="14"/>
     </row>
-    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="37"/>
       <c r="B10" s="92" t="s">
         <v>26</v>
@@ -2602,22 +2602,22 @@
       <c r="G10" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="104"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="104"/>
-      <c r="O10" s="104"/>
-      <c r="P10" s="104"/>
-      <c r="Q10" s="104"/>
-      <c r="R10" s="104"/>
-      <c r="S10" s="104"/>
-      <c r="T10" s="104"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="142"/>
+      <c r="J10" s="142"/>
+      <c r="K10" s="142"/>
+      <c r="L10" s="142"/>
+      <c r="M10" s="142"/>
+      <c r="N10" s="142"/>
+      <c r="O10" s="142"/>
+      <c r="P10" s="142"/>
+      <c r="Q10" s="142"/>
+      <c r="R10" s="142"/>
+      <c r="S10" s="142"/>
+      <c r="T10" s="142"/>
       <c r="U10" s="12"/>
     </row>
-    <row r="11" spans="1:21" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="37"/>
       <c r="B11" s="92" t="s">
         <v>27</v>
@@ -2629,22 +2629,22 @@
       <c r="G11" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="105"/>
-      <c r="L11" s="105"/>
-      <c r="M11" s="105"/>
-      <c r="N11" s="105"/>
-      <c r="O11" s="105"/>
-      <c r="P11" s="105"/>
-      <c r="Q11" s="105"/>
-      <c r="R11" s="105"/>
-      <c r="S11" s="105"/>
-      <c r="T11" s="105"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
+      <c r="O11" s="143"/>
+      <c r="P11" s="143"/>
+      <c r="Q11" s="143"/>
+      <c r="R11" s="143"/>
+      <c r="S11" s="143"/>
+      <c r="T11" s="143"/>
       <c r="U11" s="12"/>
     </row>
-    <row r="12" spans="1:21" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="37"/>
       <c r="B12" s="94" t="s">
         <v>28</v>
@@ -2656,11 +2656,11 @@
       <c r="G12" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="106"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="106"/>
+      <c r="H12" s="137"/>
+      <c r="I12" s="137"/>
+      <c r="J12" s="137"/>
+      <c r="K12" s="137"/>
+      <c r="L12" s="137"/>
       <c r="M12" s="95"/>
       <c r="N12" s="95"/>
       <c r="O12" s="95"/>
@@ -2671,7 +2671,7 @@
       <c r="T12" s="95"/>
       <c r="U12" s="13"/>
     </row>
-    <row r="13" spans="1:21" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="37"/>
       <c r="B13" s="94" t="s">
         <v>29</v>
@@ -2683,22 +2683,22 @@
       <c r="G13" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="106"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="106"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="106"/>
-      <c r="N13" s="106"/>
-      <c r="O13" s="106"/>
-      <c r="P13" s="106"/>
-      <c r="Q13" s="106"/>
-      <c r="R13" s="106"/>
-      <c r="S13" s="106"/>
-      <c r="T13" s="106"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="137"/>
+      <c r="L13" s="137"/>
+      <c r="M13" s="137"/>
+      <c r="N13" s="137"/>
+      <c r="O13" s="137"/>
+      <c r="P13" s="137"/>
+      <c r="Q13" s="137"/>
+      <c r="R13" s="137"/>
+      <c r="S13" s="137"/>
+      <c r="T13" s="137"/>
       <c r="U13" s="13"/>
     </row>
-    <row r="14" spans="1:21" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="37"/>
       <c r="B14" s="93"/>
       <c r="C14" s="93"/>
@@ -2706,22 +2706,22 @@
       <c r="E14" s="93"/>
       <c r="F14" s="93"/>
       <c r="G14" s="93"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="114"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="114"/>
-      <c r="M14" s="114"/>
-      <c r="N14" s="114"/>
-      <c r="O14" s="114"/>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="114"/>
-      <c r="R14" s="114"/>
-      <c r="S14" s="114"/>
-      <c r="T14" s="114"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="138"/>
+      <c r="L14" s="138"/>
+      <c r="M14" s="138"/>
+      <c r="N14" s="138"/>
+      <c r="O14" s="138"/>
+      <c r="P14" s="138"/>
+      <c r="Q14" s="138"/>
+      <c r="R14" s="138"/>
+      <c r="S14" s="138"/>
+      <c r="T14" s="138"/>
       <c r="U14" s="13"/>
     </row>
-    <row r="15" spans="1:21" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="37"/>
       <c r="B15" s="45"/>
       <c r="C15" s="45"/>
@@ -2744,7 +2744,7 @@
       <c r="T15" s="82"/>
       <c r="U15" s="13"/>
     </row>
-    <row r="16" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="37"/>
       <c r="B16" s="92" t="s">
         <v>31</v>
@@ -2769,7 +2769,7 @@
       <c r="T16" s="97"/>
       <c r="U16" s="29"/>
     </row>
-    <row r="17" spans="1:21" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="37"/>
       <c r="B17" s="92" t="s">
         <v>24</v>
@@ -2794,7 +2794,7 @@
       <c r="T17" s="99"/>
       <c r="U17" s="15"/>
     </row>
-    <row r="18" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="37"/>
       <c r="B18" s="92" t="s">
         <v>37</v>
@@ -2819,32 +2819,32 @@
       <c r="T18" s="98"/>
       <c r="U18" s="15"/>
     </row>
-    <row r="19" spans="1:21" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="37"/>
       <c r="B19" s="92" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="92"/>
       <c r="D19" s="92"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="106"/>
-      <c r="N19" s="106"/>
-      <c r="O19" s="106"/>
-      <c r="P19" s="106"/>
-      <c r="Q19" s="106"/>
-      <c r="R19" s="106"/>
-      <c r="S19" s="106"/>
-      <c r="T19" s="106"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
+      <c r="H19" s="137"/>
+      <c r="I19" s="137"/>
+      <c r="J19" s="137"/>
+      <c r="K19" s="137"/>
+      <c r="L19" s="137"/>
+      <c r="M19" s="137"/>
+      <c r="N19" s="137"/>
+      <c r="O19" s="137"/>
+      <c r="P19" s="137"/>
+      <c r="Q19" s="137"/>
+      <c r="R19" s="137"/>
+      <c r="S19" s="137"/>
+      <c r="T19" s="137"/>
       <c r="U19" s="15"/>
     </row>
-    <row r="20" spans="1:21" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="37"/>
       <c r="B20" s="92" t="s">
         <v>23</v>
@@ -2869,7 +2869,7 @@
       <c r="T20" s="98"/>
       <c r="U20" s="15"/>
     </row>
-    <row r="21" spans="1:21" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="37"/>
       <c r="B21" s="92" t="s">
         <v>22</v>
@@ -2881,9 +2881,9 @@
       <c r="G21" s="92"/>
       <c r="H21" s="93"/>
       <c r="I21" s="93"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="116"/>
-      <c r="L21" s="116"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="140"/>
+      <c r="L21" s="140"/>
       <c r="M21" s="93"/>
       <c r="N21" s="93"/>
       <c r="O21" s="93"/>
@@ -2894,7 +2894,7 @@
       <c r="T21" s="93"/>
       <c r="U21" s="12"/>
     </row>
-    <row r="22" spans="1:21" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="37"/>
       <c r="B22" s="92" t="s">
         <v>21</v>
@@ -2921,7 +2921,7 @@
       <c r="T22" s="93"/>
       <c r="U22" s="12"/>
     </row>
-    <row r="23" spans="1:21" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="3" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="37"/>
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
@@ -2944,135 +2944,135 @@
       <c r="T23" s="38"/>
       <c r="U23" s="12"/>
     </row>
-    <row r="24" spans="1:21" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A24" s="48"/>
       <c r="B24" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="115" t="s">
+      <c r="C24" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="115"/>
-      <c r="E24" s="115"/>
-      <c r="F24" s="115"/>
-      <c r="G24" s="115"/>
-      <c r="H24" s="115"/>
-      <c r="I24" s="115"/>
-      <c r="J24" s="115"/>
-      <c r="K24" s="115"/>
+      <c r="D24" s="139"/>
+      <c r="E24" s="139"/>
+      <c r="F24" s="139"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="139"/>
+      <c r="I24" s="139"/>
+      <c r="J24" s="139"/>
+      <c r="K24" s="139"/>
       <c r="L24" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="M24" s="115" t="s">
+      <c r="M24" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="N24" s="115"/>
-      <c r="O24" s="115"/>
-      <c r="P24" s="115" t="s">
+      <c r="N24" s="139"/>
+      <c r="O24" s="139"/>
+      <c r="P24" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="Q24" s="115"/>
-      <c r="R24" s="115"/>
-      <c r="S24" s="115" t="s">
+      <c r="Q24" s="139"/>
+      <c r="R24" s="139"/>
+      <c r="S24" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="T24" s="115"/>
+      <c r="T24" s="139"/>
       <c r="U24" s="16"/>
     </row>
-    <row r="25" spans="1:21" s="4" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" s="4" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="50"/>
       <c r="B25" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="117" t="s">
+      <c r="C25" s="135" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="117"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="117"/>
-      <c r="I25" s="117"/>
-      <c r="J25" s="117"/>
-      <c r="K25" s="117"/>
+      <c r="D25" s="135"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="135"/>
+      <c r="G25" s="135"/>
+      <c r="H25" s="135"/>
+      <c r="I25" s="135"/>
+      <c r="J25" s="135"/>
+      <c r="K25" s="135"/>
       <c r="L25" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="M25" s="117" t="s">
+      <c r="M25" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="N25" s="117"/>
-      <c r="O25" s="117"/>
-      <c r="P25" s="117" t="s">
+      <c r="N25" s="135"/>
+      <c r="O25" s="135"/>
+      <c r="P25" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="Q25" s="117"/>
-      <c r="R25" s="117"/>
-      <c r="S25" s="117" t="s">
+      <c r="Q25" s="135"/>
+      <c r="R25" s="135"/>
+      <c r="S25" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="T25" s="117"/>
+      <c r="T25" s="135"/>
       <c r="U25" s="17"/>
     </row>
-    <row r="26" spans="1:21" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="51"/>
       <c r="B26" s="79">
         <v>1</v>
       </c>
-      <c r="C26" s="118">
+      <c r="C26" s="136">
         <v>2</v>
       </c>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="118"/>
-      <c r="G26" s="118"/>
-      <c r="H26" s="118"/>
-      <c r="I26" s="118"/>
-      <c r="J26" s="118"/>
-      <c r="K26" s="118"/>
+      <c r="D26" s="136"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="136"/>
+      <c r="G26" s="136"/>
+      <c r="H26" s="136"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="136"/>
       <c r="L26" s="79">
         <v>3</v>
       </c>
-      <c r="M26" s="118">
+      <c r="M26" s="136">
         <v>4</v>
       </c>
-      <c r="N26" s="118"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="118">
+      <c r="N26" s="136"/>
+      <c r="O26" s="136"/>
+      <c r="P26" s="136">
         <v>5</v>
       </c>
-      <c r="Q26" s="118"/>
-      <c r="R26" s="118"/>
-      <c r="S26" s="118" t="s">
+      <c r="Q26" s="136"/>
+      <c r="R26" s="136"/>
+      <c r="S26" s="136" t="s">
         <v>18</v>
       </c>
-      <c r="T26" s="118"/>
+      <c r="T26" s="136"/>
       <c r="U26" s="18"/>
     </row>
-    <row r="27" spans="1:21" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="52"/>
       <c r="B27" s="83"/>
-      <c r="C27" s="130"/>
-      <c r="D27" s="131"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="131"/>
-      <c r="J27" s="131"/>
-      <c r="K27" s="132"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="113"/>
+      <c r="E27" s="113"/>
+      <c r="F27" s="113"/>
+      <c r="G27" s="113"/>
+      <c r="H27" s="113"/>
+      <c r="I27" s="113"/>
+      <c r="J27" s="113"/>
+      <c r="K27" s="114"/>
       <c r="L27" s="84"/>
-      <c r="M27" s="133"/>
-      <c r="N27" s="134"/>
-      <c r="O27" s="135"/>
-      <c r="P27" s="133"/>
-      <c r="Q27" s="134"/>
-      <c r="R27" s="135"/>
-      <c r="S27" s="136"/>
-      <c r="T27" s="137"/>
+      <c r="M27" s="115"/>
+      <c r="N27" s="116"/>
+      <c r="O27" s="117"/>
+      <c r="P27" s="115"/>
+      <c r="Q27" s="116"/>
+      <c r="R27" s="117"/>
+      <c r="S27" s="118"/>
+      <c r="T27" s="119"/>
       <c r="U27" s="30"/>
     </row>
-    <row r="28" spans="1:21" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="52"/>
       <c r="B28" s="53"/>
       <c r="C28" s="54"/>
@@ -3084,47 +3084,47 @@
       <c r="I28" s="55"/>
       <c r="J28" s="55"/>
       <c r="K28" s="55"/>
-      <c r="L28" s="140" t="s">
+      <c r="L28" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="M28" s="140"/>
-      <c r="N28" s="140"/>
-      <c r="O28" s="140"/>
-      <c r="P28" s="140"/>
-      <c r="Q28" s="140"/>
-      <c r="R28" s="141"/>
-      <c r="S28" s="142"/>
-      <c r="T28" s="143"/>
+      <c r="M28" s="122"/>
+      <c r="N28" s="122"/>
+      <c r="O28" s="122"/>
+      <c r="P28" s="122"/>
+      <c r="Q28" s="122"/>
+      <c r="R28" s="123"/>
+      <c r="S28" s="124"/>
+      <c r="T28" s="125"/>
       <c r="U28" s="31"/>
     </row>
-    <row r="29" spans="1:21" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="52"/>
-      <c r="B29" s="138" t="s">
+      <c r="B29" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="139"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
-      <c r="H29" s="139"/>
+      <c r="C29" s="121"/>
+      <c r="D29" s="121"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="121"/>
+      <c r="H29" s="121"/>
       <c r="I29" s="81"/>
       <c r="J29" s="56"/>
       <c r="K29" s="81"/>
-      <c r="L29" s="140" t="s">
+      <c r="L29" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="M29" s="140"/>
-      <c r="N29" s="140"/>
-      <c r="O29" s="140"/>
-      <c r="P29" s="140"/>
-      <c r="Q29" s="140"/>
-      <c r="R29" s="141"/>
-      <c r="S29" s="142"/>
-      <c r="T29" s="143"/>
+      <c r="M29" s="122"/>
+      <c r="N29" s="122"/>
+      <c r="O29" s="122"/>
+      <c r="P29" s="122"/>
+      <c r="Q29" s="122"/>
+      <c r="R29" s="123"/>
+      <c r="S29" s="124"/>
+      <c r="T29" s="125"/>
       <c r="U29" s="31"/>
     </row>
-    <row r="30" spans="1:21" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="52"/>
       <c r="B30" s="80"/>
       <c r="C30" s="81"/>
@@ -3136,20 +3136,20 @@
       <c r="I30" s="81"/>
       <c r="J30" s="81"/>
       <c r="K30" s="81"/>
-      <c r="L30" s="140" t="s">
+      <c r="L30" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="M30" s="140"/>
-      <c r="N30" s="140"/>
-      <c r="O30" s="140"/>
-      <c r="P30" s="140"/>
-      <c r="Q30" s="140"/>
-      <c r="R30" s="141"/>
-      <c r="S30" s="142"/>
-      <c r="T30" s="143"/>
+      <c r="M30" s="122"/>
+      <c r="N30" s="122"/>
+      <c r="O30" s="122"/>
+      <c r="P30" s="122"/>
+      <c r="Q30" s="122"/>
+      <c r="R30" s="123"/>
+      <c r="S30" s="124"/>
+      <c r="T30" s="125"/>
       <c r="U30" s="31"/>
     </row>
-    <row r="31" spans="1:21" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="48"/>
       <c r="B31" s="101" t="s">
         <v>44</v>
@@ -3160,21 +3160,21 @@
       <c r="F31" s="44"/>
       <c r="G31" s="44"/>
       <c r="H31" s="102"/>
-      <c r="I31" s="128"/>
-      <c r="J31" s="128"/>
-      <c r="K31" s="128"/>
-      <c r="L31" s="128"/>
-      <c r="M31" s="128"/>
-      <c r="N31" s="128"/>
-      <c r="O31" s="128"/>
-      <c r="P31" s="128"/>
-      <c r="Q31" s="128"/>
-      <c r="R31" s="128"/>
-      <c r="S31" s="128"/>
-      <c r="T31" s="129"/>
+      <c r="I31" s="110"/>
+      <c r="J31" s="110"/>
+      <c r="K31" s="110"/>
+      <c r="L31" s="110"/>
+      <c r="M31" s="110"/>
+      <c r="N31" s="110"/>
+      <c r="O31" s="110"/>
+      <c r="P31" s="110"/>
+      <c r="Q31" s="110"/>
+      <c r="R31" s="110"/>
+      <c r="S31" s="110"/>
+      <c r="T31" s="111"/>
       <c r="U31" s="19"/>
     </row>
-    <row r="32" spans="1:21" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="37"/>
       <c r="B32" s="57"/>
       <c r="C32" s="58"/>
@@ -3197,94 +3197,94 @@
       <c r="T32" s="60"/>
       <c r="U32" s="20"/>
     </row>
-    <row r="33" spans="1:21" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" s="7" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="61"/>
       <c r="B33" s="62"/>
-      <c r="C33" s="125" t="s">
+      <c r="C33" s="132" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="125"/>
-      <c r="E33" s="125"/>
-      <c r="F33" s="125"/>
-      <c r="G33" s="125"/>
-      <c r="H33" s="125"/>
-      <c r="I33" s="125"/>
-      <c r="J33" s="125" t="s">
+      <c r="D33" s="132"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="132"/>
+      <c r="H33" s="132"/>
+      <c r="I33" s="132"/>
+      <c r="J33" s="132" t="s">
         <v>48</v>
       </c>
-      <c r="K33" s="125"/>
-      <c r="L33" s="125"/>
-      <c r="M33" s="125"/>
-      <c r="N33" s="125" t="s">
+      <c r="K33" s="132"/>
+      <c r="L33" s="132"/>
+      <c r="M33" s="132"/>
+      <c r="N33" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="O33" s="125"/>
-      <c r="P33" s="125"/>
-      <c r="Q33" s="125"/>
-      <c r="R33" s="125"/>
-      <c r="S33" s="125"/>
-      <c r="T33" s="125"/>
+      <c r="O33" s="132"/>
+      <c r="P33" s="132"/>
+      <c r="Q33" s="132"/>
+      <c r="R33" s="132"/>
+      <c r="S33" s="132"/>
+      <c r="T33" s="132"/>
       <c r="U33" s="21"/>
     </row>
-    <row r="34" spans="1:21" s="8" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" s="8" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="63"/>
       <c r="B34" s="64"/>
-      <c r="C34" s="126" t="s">
+      <c r="C34" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="126"/>
-      <c r="E34" s="126"/>
-      <c r="F34" s="126"/>
-      <c r="G34" s="126"/>
-      <c r="H34" s="126"/>
-      <c r="I34" s="126"/>
-      <c r="J34" s="126" t="s">
+      <c r="D34" s="133"/>
+      <c r="E34" s="133"/>
+      <c r="F34" s="133"/>
+      <c r="G34" s="133"/>
+      <c r="H34" s="133"/>
+      <c r="I34" s="133"/>
+      <c r="J34" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="K34" s="126"/>
-      <c r="L34" s="126"/>
-      <c r="M34" s="126"/>
-      <c r="N34" s="126" t="s">
+      <c r="K34" s="133"/>
+      <c r="L34" s="133"/>
+      <c r="M34" s="133"/>
+      <c r="N34" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="O34" s="126"/>
-      <c r="P34" s="126"/>
-      <c r="Q34" s="126"/>
-      <c r="R34" s="126"/>
-      <c r="S34" s="126"/>
-      <c r="T34" s="126"/>
+      <c r="O34" s="133"/>
+      <c r="P34" s="133"/>
+      <c r="Q34" s="133"/>
+      <c r="R34" s="133"/>
+      <c r="S34" s="133"/>
+      <c r="T34" s="133"/>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" spans="1:21" s="9" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" s="9" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50"/>
       <c r="B35" s="65"/>
-      <c r="C35" s="127" t="s">
+      <c r="C35" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="127"/>
-      <c r="E35" s="127"/>
-      <c r="F35" s="127"/>
-      <c r="G35" s="127"/>
-      <c r="H35" s="127"/>
-      <c r="I35" s="127"/>
-      <c r="J35" s="127" t="s">
+      <c r="D35" s="134"/>
+      <c r="E35" s="134"/>
+      <c r="F35" s="134"/>
+      <c r="G35" s="134"/>
+      <c r="H35" s="134"/>
+      <c r="I35" s="134"/>
+      <c r="J35" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="K35" s="127"/>
-      <c r="L35" s="127"/>
-      <c r="M35" s="127"/>
-      <c r="N35" s="127" t="s">
+      <c r="K35" s="134"/>
+      <c r="L35" s="134"/>
+      <c r="M35" s="134"/>
+      <c r="N35" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="O35" s="127"/>
-      <c r="P35" s="127"/>
-      <c r="Q35" s="127"/>
-      <c r="R35" s="127"/>
-      <c r="S35" s="127"/>
-      <c r="T35" s="127"/>
+      <c r="O35" s="134"/>
+      <c r="P35" s="134"/>
+      <c r="Q35" s="134"/>
+      <c r="R35" s="134"/>
+      <c r="S35" s="134"/>
+      <c r="T35" s="134"/>
       <c r="U35" s="23"/>
     </row>
-    <row r="36" spans="1:21" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="37"/>
       <c r="B36" s="42"/>
       <c r="C36" s="42"/>
@@ -3307,7 +3307,7 @@
       <c r="T36" s="42"/>
       <c r="U36" s="24"/>
     </row>
-    <row r="37" spans="1:21" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A37" s="37"/>
       <c r="B37" s="38"/>
       <c r="C37" s="38"/>
@@ -3326,13 +3326,13 @@
       </c>
       <c r="O37" s="66"/>
       <c r="P37" s="66"/>
-      <c r="Q37" s="119"/>
-      <c r="R37" s="119"/>
-      <c r="S37" s="119"/>
-      <c r="T37" s="120"/>
+      <c r="Q37" s="126"/>
+      <c r="R37" s="126"/>
+      <c r="S37" s="126"/>
+      <c r="T37" s="127"/>
       <c r="U37" s="25"/>
     </row>
-    <row r="38" spans="1:21" s="10" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" s="10" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="67"/>
       <c r="B38" s="68"/>
       <c r="C38" s="68"/>
@@ -3346,27 +3346,27 @@
       <c r="K38" s="69"/>
       <c r="L38" s="69"/>
       <c r="M38" s="68"/>
-      <c r="N38" s="121" t="s">
+      <c r="N38" s="128" t="s">
         <v>41</v>
       </c>
-      <c r="O38" s="122"/>
-      <c r="P38" s="122"/>
-      <c r="Q38" s="123"/>
-      <c r="R38" s="123"/>
-      <c r="S38" s="123"/>
-      <c r="T38" s="124"/>
+      <c r="O38" s="129"/>
+      <c r="P38" s="129"/>
+      <c r="Q38" s="130"/>
+      <c r="R38" s="130"/>
+      <c r="S38" s="130"/>
+      <c r="T38" s="131"/>
       <c r="U38" s="26"/>
     </row>
-    <row r="39" spans="1:21" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="37"/>
       <c r="B39" s="70"/>
-      <c r="C39" s="149"/>
-      <c r="D39" s="149"/>
-      <c r="E39" s="149"/>
-      <c r="F39" s="149"/>
-      <c r="G39" s="149"/>
-      <c r="H39" s="149"/>
-      <c r="I39" s="149"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="109"/>
+      <c r="E39" s="109"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="109"/>
+      <c r="H39" s="109"/>
+      <c r="I39" s="109"/>
       <c r="J39" s="42"/>
       <c r="K39" s="42"/>
       <c r="L39" s="42"/>
@@ -3376,13 +3376,13 @@
       </c>
       <c r="O39" s="87"/>
       <c r="P39" s="71"/>
-      <c r="Q39" s="144"/>
-      <c r="R39" s="144"/>
-      <c r="S39" s="144"/>
-      <c r="T39" s="145"/>
+      <c r="Q39" s="103"/>
+      <c r="R39" s="103"/>
+      <c r="S39" s="103"/>
+      <c r="T39" s="104"/>
       <c r="U39" s="27"/>
     </row>
-    <row r="40" spans="1:21" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="37"/>
       <c r="B40" s="74"/>
       <c r="C40" s="73"/>
@@ -3405,7 +3405,7 @@
       <c r="T40" s="42"/>
       <c r="U40" s="24"/>
     </row>
-    <row r="41" spans="1:21" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="37"/>
       <c r="B41" s="74" t="s">
         <v>33</v>
@@ -3415,11 +3415,11 @@
       <c r="E41" s="75"/>
       <c r="F41" s="75"/>
       <c r="G41" s="75"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
-      <c r="L41" s="146"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="105"/>
+      <c r="K41" s="105"/>
+      <c r="L41" s="105"/>
       <c r="M41" s="38"/>
       <c r="N41" s="72"/>
       <c r="O41" s="42"/>
@@ -3430,22 +3430,22 @@
       <c r="T41" s="42"/>
       <c r="U41" s="24"/>
     </row>
-    <row r="42" spans="1:21" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="37"/>
-      <c r="B42" s="147" t="s">
+      <c r="B42" s="106" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="147"/>
-      <c r="D42" s="147"/>
-      <c r="E42" s="147"/>
-      <c r="F42" s="147"/>
-      <c r="G42" s="147"/>
-      <c r="H42" s="147"/>
-      <c r="I42" s="147"/>
-      <c r="J42" s="147"/>
-      <c r="K42" s="147"/>
-      <c r="L42" s="147"/>
-      <c r="M42" s="147"/>
+      <c r="C42" s="106"/>
+      <c r="D42" s="106"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="106"/>
+      <c r="G42" s="106"/>
+      <c r="H42" s="106"/>
+      <c r="I42" s="106"/>
+      <c r="J42" s="106"/>
+      <c r="K42" s="106"/>
+      <c r="L42" s="106"/>
+      <c r="M42" s="106"/>
       <c r="N42" s="72"/>
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
@@ -3455,64 +3455,99 @@
       <c r="T42" s="42"/>
       <c r="U42" s="24"/>
     </row>
-    <row r="43" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="76"/>
-      <c r="B43" s="148" t="s">
+      <c r="B43" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="148"/>
-      <c r="D43" s="148"/>
-      <c r="E43" s="148"/>
-      <c r="F43" s="148"/>
-      <c r="G43" s="148"/>
-      <c r="H43" s="148"/>
-      <c r="I43" s="148"/>
-      <c r="J43" s="148"/>
-      <c r="K43" s="148"/>
-      <c r="L43" s="148"/>
-      <c r="M43" s="148"/>
-      <c r="N43" s="148"/>
-      <c r="O43" s="148"/>
-      <c r="P43" s="148"/>
-      <c r="Q43" s="148"/>
-      <c r="R43" s="148"/>
-      <c r="S43" s="148"/>
-      <c r="T43" s="148"/>
+      <c r="C43" s="107"/>
+      <c r="D43" s="107"/>
+      <c r="E43" s="107"/>
+      <c r="F43" s="107"/>
+      <c r="G43" s="107"/>
+      <c r="H43" s="107"/>
+      <c r="I43" s="107"/>
+      <c r="J43" s="107"/>
+      <c r="K43" s="107"/>
+      <c r="L43" s="107"/>
+      <c r="M43" s="107"/>
+      <c r="N43" s="107"/>
+      <c r="O43" s="107"/>
+      <c r="P43" s="107"/>
+      <c r="Q43" s="107"/>
+      <c r="R43" s="107"/>
+      <c r="S43" s="107"/>
+      <c r="T43" s="107"/>
       <c r="U43" s="28"/>
     </row>
-    <row r="44" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="38"/>
-      <c r="B44" s="111" t="s">
+      <c r="B44" s="108" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="111"/>
-      <c r="D44" s="111"/>
-      <c r="E44" s="111"/>
-      <c r="F44" s="111"/>
-      <c r="G44" s="111"/>
-      <c r="H44" s="111"/>
-      <c r="I44" s="111"/>
-      <c r="J44" s="111"/>
-      <c r="K44" s="111"/>
-      <c r="L44" s="111"/>
-      <c r="M44" s="111"/>
-      <c r="N44" s="111"/>
-      <c r="O44" s="111"/>
-      <c r="P44" s="111"/>
-      <c r="Q44" s="111"/>
-      <c r="R44" s="111"/>
-      <c r="S44" s="111"/>
-      <c r="T44" s="111"/>
+      <c r="C44" s="108"/>
+      <c r="D44" s="108"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="108"/>
+      <c r="H44" s="108"/>
+      <c r="I44" s="108"/>
+      <c r="J44" s="108"/>
+      <c r="K44" s="108"/>
+      <c r="L44" s="108"/>
+      <c r="M44" s="108"/>
+      <c r="N44" s="108"/>
+      <c r="O44" s="108"/>
+      <c r="P44" s="108"/>
+      <c r="Q44" s="108"/>
+      <c r="R44" s="108"/>
+      <c r="S44" s="108"/>
+      <c r="T44" s="108"/>
       <c r="U44" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="Q39:T39"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="B42:M42"/>
-    <mergeCell ref="B43:T43"/>
-    <mergeCell ref="B44:T44"/>
-    <mergeCell ref="C39:I39"/>
+    <mergeCell ref="H9:T9"/>
+    <mergeCell ref="H10:T10"/>
+    <mergeCell ref="H11:T11"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="H2:O2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="H3:O3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="H4:O4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H7:O7"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:T13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:T14"/>
+    <mergeCell ref="C24:K24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="E19:T19"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="C25:K25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="P25:R25"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="C26:K26"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="Q37:T37"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="Q38:T38"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="N33:T33"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="N34:T34"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="N35:T35"/>
     <mergeCell ref="I31:T31"/>
     <mergeCell ref="C27:K27"/>
     <mergeCell ref="M27:O27"/>
@@ -3525,47 +3560,12 @@
     <mergeCell ref="S30:T30"/>
     <mergeCell ref="L28:R28"/>
     <mergeCell ref="S28:T28"/>
-    <mergeCell ref="Q37:T37"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="Q38:T38"/>
-    <mergeCell ref="C33:I33"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="N33:T33"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="N34:T34"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="N35:T35"/>
-    <mergeCell ref="C25:K25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="P25:R25"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="C26:K26"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="P26:R26"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:T13"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:T14"/>
-    <mergeCell ref="C24:K24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="E19:T19"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="H9:T9"/>
-    <mergeCell ref="H10:T10"/>
-    <mergeCell ref="H11:T11"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="H2:O2"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="H3:O3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="H4:O4"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="H7:O7"/>
+    <mergeCell ref="Q39:T39"/>
+    <mergeCell ref="B42:M42"/>
+    <mergeCell ref="B43:T43"/>
+    <mergeCell ref="B44:T44"/>
+    <mergeCell ref="C39:I39"/>
+    <mergeCell ref="H41:L41"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0" header="0.25" footer="0"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>
